--- a/LangMod/EN/Zones.xlsx
+++ b/LangMod/EN/Zones.xlsx
@@ -137,7 +137,7 @@
     <t xml:space="preserve">Battlefield</t>
   </si>
   <si>
-    <t xml:space="preserve">Zone_Arena</t>
+    <t xml:space="preserve">Zone_Arena_RQX</t>
   </si>
   <si>
     <r>
@@ -666,7 +666,7 @@
     <t xml:space="preserve">Manufacturing Site</t>
   </si>
   <si>
-    <t xml:space="preserve">Zone_Harvest</t>
+    <t xml:space="preserve">Zone_Harvest_RQX</t>
   </si>
   <si>
     <t xml:space="preserve">instance_guild_merchant</t>
@@ -869,7 +869,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -887,6 +887,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1147,7 +1151,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="59.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="5" style="1" width="7.43"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="1" width="7.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="12" style="1" width="7.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16336" style="1" width="11.53"/>
@@ -1333,7 +1338,7 @@
       <c r="D4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F4" s="2" t="n">
@@ -1345,7 +1350,7 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>32</v>
       </c>
       <c r="L4" s="2" t="s">
@@ -1421,7 +1426,7 @@
       <c r="D5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F5" s="2" t="n">
@@ -1433,7 +1438,7 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="6" t="s">
         <v>36</v>
       </c>
       <c r="L5" s="2" t="s">
@@ -1508,7 +1513,7 @@
       <c r="D6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="2" t="n">
@@ -1520,7 +1525,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="6" t="s">
         <v>38</v>
       </c>
       <c r="L6" s="2" t="s">
@@ -1595,7 +1600,7 @@
       <c r="D7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="2" t="n">
@@ -1607,7 +1612,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L7" s="2" t="s">
@@ -1682,7 +1687,7 @@
       <c r="D8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F8" s="2" t="n">
@@ -1694,7 +1699,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="6" t="s">
         <v>42</v>
       </c>
       <c r="L8" s="2" t="s">
@@ -1769,7 +1774,7 @@
       <c r="D9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F9" s="2" t="n">
@@ -1781,7 +1786,7 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="6" t="s">
         <v>44</v>
       </c>
       <c r="L9" s="2" t="s">
@@ -1856,7 +1861,7 @@
       <c r="D10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="2" t="n">
@@ -1868,7 +1873,7 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="6" t="s">
         <v>46</v>
       </c>
       <c r="L10" s="2" t="s">
@@ -1943,7 +1948,7 @@
       <c r="D11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F11" s="2" t="n">
@@ -1955,7 +1960,7 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="6" t="s">
         <v>48</v>
       </c>
       <c r="L11" s="2" t="s">
@@ -2030,7 +2035,7 @@
       <c r="D12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F12" s="2" t="n">
@@ -2042,7 +2047,7 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="6" t="s">
         <v>50</v>
       </c>
       <c r="L12" s="2" t="s">
@@ -2117,7 +2122,7 @@
       <c r="D13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F13" s="2" t="n">
@@ -2129,7 +2134,7 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="6" t="s">
         <v>52</v>
       </c>
       <c r="L13" s="2" t="s">
@@ -2204,7 +2209,7 @@
       <c r="D14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F14" s="2" t="n">
@@ -2291,7 +2296,7 @@
       <c r="D15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F15" s="2" t="n">
@@ -2303,7 +2308,7 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="6" t="s">
         <v>56</v>
       </c>
       <c r="L15" s="2" t="s">
@@ -2378,7 +2383,7 @@
       <c r="D16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F16" s="2" t="n">
@@ -2390,7 +2395,7 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="6" t="s">
         <v>58</v>
       </c>
       <c r="L16" s="2" t="s">
@@ -2465,7 +2470,7 @@
       <c r="D17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F17" s="2" t="n">
@@ -2477,7 +2482,7 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="6" t="s">
         <v>60</v>
       </c>
       <c r="L17" s="2" t="s">
@@ -2552,7 +2557,7 @@
       <c r="D18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F18" s="2" t="n">
@@ -2564,7 +2569,7 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="6" t="s">
         <v>62</v>
       </c>
       <c r="L18" s="2" t="s">
@@ -2639,7 +2644,7 @@
       <c r="D19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F19" s="2" t="n">
@@ -2651,7 +2656,7 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="6" t="s">
         <v>64</v>
       </c>
       <c r="L19" s="2" t="s">
@@ -2738,7 +2743,7 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K20" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L20" s="2" t="s">
@@ -2753,68 +2758,68 @@
       <c r="R20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="XDH20" s="0"/>
-      <c r="XDI20" s="0"/>
-      <c r="XDJ20" s="0"/>
-      <c r="XDK20" s="0"/>
-      <c r="XDL20" s="0"/>
-      <c r="XDM20" s="0"/>
-      <c r="XDN20" s="0"/>
-      <c r="XDO20" s="0"/>
-      <c r="XDP20" s="0"/>
-      <c r="XDQ20" s="0"/>
-      <c r="XDR20" s="0"/>
-      <c r="XDS20" s="0"/>
-      <c r="XDT20" s="0"/>
-      <c r="XDU20" s="0"/>
-      <c r="XDV20" s="0"/>
-      <c r="XDW20" s="0"/>
-      <c r="XDX20" s="0"/>
-      <c r="XDY20" s="0"/>
-      <c r="XDZ20" s="0"/>
-      <c r="XEA20" s="0"/>
-      <c r="XEB20" s="0"/>
-      <c r="XEC20" s="0"/>
-      <c r="XED20" s="0"/>
-      <c r="XEE20" s="0"/>
-      <c r="XEF20" s="0"/>
-      <c r="XEG20" s="0"/>
-      <c r="XEH20" s="0"/>
-      <c r="XEI20" s="0"/>
-      <c r="XEJ20" s="0"/>
-      <c r="XEK20" s="0"/>
-      <c r="XEL20" s="0"/>
-      <c r="XEM20" s="0"/>
-      <c r="XEN20" s="0"/>
-      <c r="XEO20" s="0"/>
-      <c r="XEP20" s="0"/>
-      <c r="XEQ20" s="0"/>
-      <c r="XER20" s="0"/>
-      <c r="XES20" s="0"/>
-      <c r="XET20" s="0"/>
-      <c r="XEU20" s="0"/>
-      <c r="XEV20" s="0"/>
-      <c r="XEW20" s="0"/>
-      <c r="XEX20" s="0"/>
-      <c r="XEY20" s="0"/>
-      <c r="XEZ20" s="0"/>
-      <c r="XFA20" s="0"/>
-      <c r="XFB20" s="0"/>
-      <c r="XFC20" s="0"/>
-      <c r="XFD20" s="0"/>
+      <c r="XDH20" s="1"/>
+      <c r="XDI20" s="1"/>
+      <c r="XDJ20" s="1"/>
+      <c r="XDK20" s="1"/>
+      <c r="XDL20" s="1"/>
+      <c r="XDM20" s="1"/>
+      <c r="XDN20" s="1"/>
+      <c r="XDO20" s="1"/>
+      <c r="XDP20" s="1"/>
+      <c r="XDQ20" s="1"/>
+      <c r="XDR20" s="1"/>
+      <c r="XDS20" s="1"/>
+      <c r="XDT20" s="1"/>
+      <c r="XDU20" s="1"/>
+      <c r="XDV20" s="1"/>
+      <c r="XDW20" s="1"/>
+      <c r="XDX20" s="1"/>
+      <c r="XDY20" s="1"/>
+      <c r="XDZ20" s="1"/>
+      <c r="XEA20" s="1"/>
+      <c r="XEB20" s="1"/>
+      <c r="XEC20" s="1"/>
+      <c r="XED20" s="1"/>
+      <c r="XEE20" s="1"/>
+      <c r="XEF20" s="1"/>
+      <c r="XEG20" s="1"/>
+      <c r="XEH20" s="1"/>
+      <c r="XEI20" s="1"/>
+      <c r="XEJ20" s="1"/>
+      <c r="XEK20" s="1"/>
+      <c r="XEL20" s="1"/>
+      <c r="XEM20" s="1"/>
+      <c r="XEN20" s="1"/>
+      <c r="XEO20" s="1"/>
+      <c r="XEP20" s="1"/>
+      <c r="XEQ20" s="1"/>
+      <c r="XER20" s="1"/>
+      <c r="XES20" s="1"/>
+      <c r="XET20" s="1"/>
+      <c r="XEU20" s="1"/>
+      <c r="XEV20" s="1"/>
+      <c r="XEW20" s="1"/>
+      <c r="XEX20" s="1"/>
+      <c r="XEY20" s="1"/>
+      <c r="XEZ20" s="1"/>
+      <c r="XFA20" s="1"/>
+      <c r="XFB20" s="1"/>
+      <c r="XFC20" s="1"/>
+      <c r="XFD20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="6"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="4" t="s">
         <v>70</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F21" s="2" t="n">
@@ -2853,17 +2858,17 @@
       <c r="W21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="6"/>
+      <c r="B22" s="7"/>
       <c r="C22" s="4" t="s">
         <v>74</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F22" s="2" t="n">
@@ -2902,17 +2907,17 @@
       <c r="W22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="6"/>
+      <c r="B23" s="7"/>
       <c r="C23" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F23" s="2" t="n">
@@ -2951,7 +2956,7 @@
       <c r="W23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="8" t="s">
         <v>81</v>
       </c>
       <c r="B24" s="4"/>
@@ -2961,7 +2966,7 @@
       <c r="D24" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F24" s="2" t="n">
@@ -2970,20 +2975,20 @@
       <c r="G24" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H24" s="8"/>
+      <c r="H24" s="9"/>
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8" t="s">
+      <c r="J24" s="9"/>
+      <c r="K24" s="9" t="s">
         <v>84</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="8"/>
+      <c r="M24" s="9"/>
       <c r="N24" s="2"/>
-      <c r="O24" s="8"/>
+      <c r="O24" s="9"/>
       <c r="P24" s="2" t="n">
         <v>0</v>
       </c>
@@ -2993,141 +2998,141 @@
       <c r="R24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
-      <c r="B26" s="6"/>
+      <c r="B26" s="7"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
-      <c r="B27" s="6"/>
+      <c r="B27" s="7"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
+      <c r="V27" s="10"/>
+      <c r="W27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
-      <c r="B28" s="6"/>
+      <c r="B28" s="7"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10"/>
+      <c r="V28" s="10"/>
+      <c r="W28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
-      <c r="C30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3176,7 +3181,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
-      <c r="B32" s="6"/>
+      <c r="B32" s="7"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -3202,7 +3207,7 @@
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
-      <c r="C33" s="6"/>
+      <c r="C33" s="7"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -3254,50 +3259,50 @@
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
+      <c r="V35" s="10"/>
+      <c r="W35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
-      <c r="S36" s="9"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10"/>
+      <c r="V36" s="10"/>
+      <c r="W36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
@@ -3379,50 +3384,50 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="9"/>
-      <c r="R40" s="9"/>
-      <c r="S40" s="9"/>
-      <c r="T40" s="9"/>
-      <c r="U40" s="9"/>
-      <c r="V40" s="9"/>
-      <c r="W40" s="9"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
+      <c r="U40" s="10"/>
+      <c r="V40" s="10"/>
+      <c r="W40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
+      <c r="V41" s="10"/>
+      <c r="W41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
@@ -3477,7 +3482,7 @@
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="4"/>
-      <c r="C44" s="6"/>
+      <c r="C44" s="7"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -3526,382 +3531,382 @@
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
       <c r="D46" s="4"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
-      <c r="O46" s="9"/>
-      <c r="P46" s="9"/>
-      <c r="Q46" s="9"/>
-      <c r="R46" s="9"/>
-      <c r="S46" s="9"/>
-      <c r="T46" s="9"/>
-      <c r="U46" s="9"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="9"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
+      <c r="U46" s="10"/>
+      <c r="V46" s="10"/>
+      <c r="W46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9"/>
-      <c r="N47" s="9"/>
-      <c r="O47" s="9"/>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="9"/>
-      <c r="R47" s="9"/>
-      <c r="S47" s="9"/>
-      <c r="T47" s="9"/>
-      <c r="U47" s="9"/>
-      <c r="V47" s="9"/>
-      <c r="W47" s="9"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
+      <c r="V47" s="10"/>
+      <c r="W47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-      <c r="M48" s="9"/>
-      <c r="N48" s="9"/>
-      <c r="O48" s="9"/>
-      <c r="P48" s="9"/>
-      <c r="Q48" s="9"/>
-      <c r="R48" s="9"/>
-      <c r="S48" s="9"/>
-      <c r="T48" s="9"/>
-      <c r="U48" s="9"/>
-      <c r="V48" s="9"/>
-      <c r="W48" s="9"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="10"/>
+      <c r="U48" s="10"/>
+      <c r="V48" s="10"/>
+      <c r="W48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-      <c r="M49" s="9"/>
-      <c r="N49" s="9"/>
-      <c r="O49" s="9"/>
-      <c r="P49" s="9"/>
-      <c r="Q49" s="9"/>
-      <c r="R49" s="9"/>
-      <c r="S49" s="9"/>
-      <c r="T49" s="9"/>
-      <c r="U49" s="9"/>
-      <c r="V49" s="9"/>
-      <c r="W49" s="9"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10"/>
+      <c r="V49" s="10"/>
+      <c r="W49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="9"/>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9"/>
-      <c r="Q50" s="9"/>
-      <c r="R50" s="9"/>
-      <c r="S50" s="9"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="10"/>
+      <c r="T50" s="10"/>
+      <c r="U50" s="10"/>
+      <c r="V50" s="10"/>
+      <c r="W50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="9"/>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="9"/>
-      <c r="R51" s="9"/>
-      <c r="S51" s="9"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
+      <c r="V51" s="10"/>
+      <c r="W51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
-      <c r="N52" s="9"/>
-      <c r="O52" s="9"/>
-      <c r="P52" s="9"/>
-      <c r="Q52" s="9"/>
-      <c r="R52" s="9"/>
-      <c r="S52" s="9"/>
-      <c r="T52" s="9"/>
-      <c r="U52" s="9"/>
-      <c r="V52" s="9"/>
-      <c r="W52" s="9"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="10"/>
+      <c r="U52" s="10"/>
+      <c r="V52" s="10"/>
+      <c r="W52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-      <c r="M53" s="9"/>
-      <c r="N53" s="9"/>
-      <c r="O53" s="9"/>
-      <c r="P53" s="9"/>
-      <c r="Q53" s="9"/>
-      <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
-      <c r="T53" s="9"/>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
+      <c r="V53" s="10"/>
+      <c r="W53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
-      <c r="N54" s="9"/>
-      <c r="O54" s="9"/>
-      <c r="P54" s="9"/>
-      <c r="Q54" s="9"/>
-      <c r="R54" s="9"/>
-      <c r="S54" s="9"/>
-      <c r="T54" s="9"/>
-      <c r="U54" s="9"/>
-      <c r="V54" s="9"/>
-      <c r="W54" s="9"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
+      <c r="S54" s="10"/>
+      <c r="T54" s="10"/>
+      <c r="U54" s="10"/>
+      <c r="V54" s="10"/>
+      <c r="W54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-      <c r="M55" s="9"/>
-      <c r="N55" s="9"/>
-      <c r="O55" s="9"/>
-      <c r="P55" s="9"/>
-      <c r="Q55" s="9"/>
-      <c r="R55" s="9"/>
-      <c r="S55" s="9"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="10"/>
+      <c r="U55" s="10"/>
+      <c r="V55" s="10"/>
+      <c r="W55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-      <c r="M56" s="9"/>
-      <c r="N56" s="9"/>
-      <c r="O56" s="9"/>
-      <c r="P56" s="9"/>
-      <c r="Q56" s="9"/>
-      <c r="R56" s="9"/>
-      <c r="S56" s="9"/>
-      <c r="T56" s="9"/>
-      <c r="U56" s="9"/>
-      <c r="V56" s="9"/>
-      <c r="W56" s="9"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="10"/>
+      <c r="V56" s="10"/>
+      <c r="W56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
-      <c r="M57" s="9"/>
-      <c r="N57" s="9"/>
-      <c r="O57" s="9"/>
-      <c r="P57" s="9"/>
-      <c r="Q57" s="9"/>
-      <c r="R57" s="9"/>
-      <c r="S57" s="9"/>
-      <c r="T57" s="9"/>
-      <c r="U57" s="9"/>
-      <c r="V57" s="9"/>
-      <c r="W57" s="9"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
+      <c r="S57" s="10"/>
+      <c r="T57" s="10"/>
+      <c r="U57" s="10"/>
+      <c r="V57" s="10"/>
+      <c r="W57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
-      <c r="M58" s="9"/>
-      <c r="N58" s="9"/>
-      <c r="O58" s="9"/>
-      <c r="P58" s="9"/>
-      <c r="Q58" s="9"/>
-      <c r="R58" s="9"/>
-      <c r="S58" s="9"/>
-      <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="10"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
+      <c r="S58" s="10"/>
+      <c r="T58" s="10"/>
+      <c r="U58" s="10"/>
+      <c r="V58" s="10"/>
+      <c r="W58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="9"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="9"/>
-      <c r="M59" s="9"/>
-      <c r="N59" s="9"/>
-      <c r="O59" s="9"/>
-      <c r="P59" s="9"/>
-      <c r="Q59" s="9"/>
-      <c r="R59" s="9"/>
-      <c r="S59" s="9"/>
-      <c r="T59" s="9"/>
-      <c r="U59" s="9"/>
-      <c r="V59" s="9"/>
-      <c r="W59" s="9"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="10"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="10"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
+      <c r="V59" s="10"/>
+      <c r="W59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
-      <c r="B60" s="6"/>
+      <c r="B60" s="7"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="9"/>
-      <c r="J60" s="9"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="9"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="9"/>
-      <c r="O60" s="9"/>
-      <c r="P60" s="9"/>
-      <c r="Q60" s="9"/>
-      <c r="R60" s="9"/>
-      <c r="S60" s="9"/>
-      <c r="T60" s="9"/>
-      <c r="U60" s="9"/>
-      <c r="V60" s="9"/>
-      <c r="W60" s="9"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="10"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="10"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
+      <c r="S60" s="10"/>
+      <c r="T60" s="10"/>
+      <c r="U60" s="10"/>
+      <c r="V60" s="10"/>
+      <c r="W60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
-      <c r="B61" s="6"/>
+      <c r="B61" s="7"/>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -3951,7 +3956,7 @@
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3"/>
-      <c r="B63" s="6"/>
+      <c r="B63" s="7"/>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -3976,7 +3981,7 @@
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3"/>
-      <c r="B64" s="6"/>
+      <c r="B64" s="7"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -4001,7 +4006,7 @@
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
-      <c r="B65" s="6"/>
+      <c r="B65" s="7"/>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -4026,7 +4031,7 @@
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
-      <c r="B66" s="6"/>
+      <c r="B66" s="7"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -4202,7 +4207,7 @@
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3"/>
       <c r="B73" s="4"/>
-      <c r="C73" s="6"/>
+      <c r="C73" s="7"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
@@ -4526,7 +4531,7 @@
     </row>
     <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3"/>
-      <c r="B86" s="6"/>
+      <c r="B86" s="7"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -4626,7 +4631,7 @@
     </row>
     <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3"/>
-      <c r="B90" s="6"/>
+      <c r="B90" s="7"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -4651,7 +4656,7 @@
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3"/>
-      <c r="B91" s="6"/>
+      <c r="B91" s="7"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -4676,7 +4681,7 @@
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3"/>
-      <c r="B92" s="6"/>
+      <c r="B92" s="7"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -4701,7 +4706,7 @@
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3"/>
-      <c r="B93" s="6"/>
+      <c r="B93" s="7"/>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -4726,7 +4731,7 @@
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3"/>
-      <c r="B94" s="6"/>
+      <c r="B94" s="7"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -4751,7 +4756,7 @@
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3"/>
-      <c r="B95" s="6"/>
+      <c r="B95" s="7"/>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -4776,7 +4781,7 @@
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3"/>
-      <c r="B96" s="6"/>
+      <c r="B96" s="7"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -4801,7 +4806,7 @@
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3"/>
-      <c r="B97" s="6"/>
+      <c r="B97" s="7"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -4826,7 +4831,7 @@
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3"/>
-      <c r="B98" s="6"/>
+      <c r="B98" s="7"/>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -4851,7 +4856,7 @@
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3"/>
-      <c r="B99" s="6"/>
+      <c r="B99" s="7"/>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -4876,7 +4881,7 @@
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3"/>
-      <c r="B100" s="6"/>
+      <c r="B100" s="7"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -4926,7 +4931,7 @@
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3"/>
-      <c r="B102" s="6"/>
+      <c r="B102" s="7"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -4951,7 +4956,7 @@
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3"/>
-      <c r="B103" s="6"/>
+      <c r="B103" s="7"/>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -4976,7 +4981,7 @@
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3"/>
-      <c r="B104" s="6"/>
+      <c r="B104" s="7"/>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -5351,7 +5356,7 @@
     </row>
     <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3"/>
-      <c r="B119" s="6"/>
+      <c r="B119" s="7"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -5376,7 +5381,7 @@
     </row>
     <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3"/>
-      <c r="B120" s="6"/>
+      <c r="B120" s="7"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
@@ -5426,7 +5431,7 @@
     </row>
     <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3"/>
-      <c r="B122" s="6"/>
+      <c r="B122" s="7"/>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
@@ -5451,7 +5456,7 @@
     </row>
     <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3"/>
-      <c r="B123" s="6"/>
+      <c r="B123" s="7"/>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
@@ -5476,7 +5481,7 @@
     </row>
     <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3"/>
-      <c r="B124" s="6"/>
+      <c r="B124" s="7"/>
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
@@ -5501,7 +5506,7 @@
     </row>
     <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3"/>
-      <c r="B125" s="6"/>
+      <c r="B125" s="7"/>
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
@@ -5526,7 +5531,7 @@
     </row>
     <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3"/>
-      <c r="B126" s="6"/>
+      <c r="B126" s="7"/>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -5551,7 +5556,7 @@
     </row>
     <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3"/>
-      <c r="B127" s="6"/>
+      <c r="B127" s="7"/>
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -5576,7 +5581,7 @@
     </row>
     <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3"/>
-      <c r="B128" s="10"/>
+      <c r="B128" s="11"/>
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -5601,7 +5606,7 @@
     </row>
     <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3"/>
-      <c r="B129" s="6"/>
+      <c r="B129" s="7"/>
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -5626,7 +5631,7 @@
     </row>
     <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3"/>
-      <c r="B130" s="6"/>
+      <c r="B130" s="7"/>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
@@ -5651,7 +5656,7 @@
     </row>
     <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3"/>
-      <c r="B131" s="6"/>
+      <c r="B131" s="7"/>
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
@@ -5676,7 +5681,7 @@
     </row>
     <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3"/>
-      <c r="B132" s="6"/>
+      <c r="B132" s="7"/>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
@@ -5701,7 +5706,7 @@
     </row>
     <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3"/>
-      <c r="B133" s="6"/>
+      <c r="B133" s="7"/>
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
@@ -5726,7 +5731,7 @@
     </row>
     <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3"/>
-      <c r="B134" s="6"/>
+      <c r="B134" s="7"/>
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
@@ -5751,7 +5756,7 @@
     </row>
     <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3"/>
-      <c r="B135" s="6"/>
+      <c r="B135" s="7"/>
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
@@ -6901,7 +6906,7 @@
     </row>
     <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3"/>
-      <c r="B181" s="11"/>
+      <c r="B181" s="12"/>
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -7051,7 +7056,7 @@
     </row>
     <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3"/>
-      <c r="B187" s="11"/>
+      <c r="B187" s="12"/>
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -7076,7 +7081,7 @@
     </row>
     <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3"/>
-      <c r="B188" s="11"/>
+      <c r="B188" s="12"/>
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -7101,7 +7106,7 @@
     </row>
     <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3"/>
-      <c r="B189" s="11"/>
+      <c r="B189" s="12"/>
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -16450,7 +16455,7 @@
       <c r="W562" s="4"/>
     </row>
     <row r="563" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A563" s="12"/>
+      <c r="A563" s="13"/>
       <c r="B563" s="4"/>
       <c r="C563" s="4"/>
       <c r="D563" s="4"/>
@@ -16475,7 +16480,7 @@
       <c r="W563" s="4"/>
     </row>
     <row r="564" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A564" s="12"/>
+      <c r="A564" s="13"/>
       <c r="B564" s="4"/>
       <c r="C564" s="4"/>
       <c r="D564" s="4"/>
@@ -17651,7 +17656,7 @@
     </row>
     <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="3"/>
-      <c r="B611" s="6"/>
+      <c r="B611" s="7"/>
       <c r="C611" s="4"/>
       <c r="D611" s="4"/>
       <c r="E611" s="4"/>
@@ -18851,7 +18856,7 @@
     </row>
     <row r="659" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="3"/>
-      <c r="B659" s="11"/>
+      <c r="B659" s="12"/>
       <c r="C659" s="4"/>
       <c r="D659" s="4"/>
       <c r="E659" s="4"/>
@@ -18876,7 +18881,7 @@
     </row>
     <row r="660" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="3"/>
-      <c r="B660" s="13"/>
+      <c r="B660" s="14"/>
       <c r="C660" s="4"/>
       <c r="D660" s="4"/>
       <c r="E660" s="4"/>
@@ -19800,7 +19805,7 @@
       <c r="W696" s="4"/>
     </row>
     <row r="697" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A697" s="14"/>
+      <c r="A697" s="15"/>
       <c r="B697" s="4"/>
       <c r="C697" s="4"/>
       <c r="D697" s="4"/>

--- a/LangMod/EN/Zones.xlsx
+++ b/LangMod/EN/Zones.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="126">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -716,6 +716,369 @@
   <si>
     <t xml:space="preserve">guild_mage_kantan</t>
   </si>
+  <si>
+    <t xml:space="preserve">instance_cave0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">洞窟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone_Arena_Cave_RQX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cave_instance0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance_cave1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cave_instance1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance_cave2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cave_instance2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_rqx_dungeon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZoneRandomQuestNefia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lesimas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rqxrandomquest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,0,322</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">byakko_mod_rqx_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">dungeon_plain</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">草原</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grassland</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">RandomQuest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NefiaPlain</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DungeonForest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plain</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">byakko_mod_rqx_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">dungeon_forest</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">森</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forest</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">RandomQuest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NefiaForest</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon_Forest</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">byakko_mod_rqx_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">dungeon_ruin</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">遺跡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruin</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">RandomQuest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Nefia</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">byakko_mod_rqx_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">dungeon_water</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">海底遺跡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Underwater Ruin</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">RandomQuest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NefiaWater</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DungeonWater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon_Water</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">byakko_mod_rqx_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">dungeon_factory</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">機械遺跡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machinarium</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">RandomQuest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NefiaFactory</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DungeonFactory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon_Factory</t>
+  </si>
 </sst>
 </file>
 
@@ -724,7 +1087,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -791,6 +1154,13 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -869,7 +1239,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -910,11 +1280,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -922,15 +1296,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1151,7 +1525,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="59.58"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="1" width="7.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="12" style="1" width="7.43"/>
@@ -3004,230 +3378,549 @@
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
-      <c r="U26" s="10"/>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
-      <c r="T27" s="10"/>
-      <c r="U27" s="10"/>
-      <c r="V27" s="10"/>
-      <c r="W27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
-      <c r="S28" s="10"/>
-      <c r="T28" s="10"/>
-      <c r="U28" s="10"/>
-      <c r="V28" s="10"/>
-      <c r="W28" s="10"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10"/>
-      <c r="T29" s="10"/>
-      <c r="U29" s="10"/>
-      <c r="V29" s="10"/>
-      <c r="W29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
+    <row r="25" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="XDH25" s="1"/>
+      <c r="XDI25" s="1"/>
+      <c r="XDJ25" s="1"/>
+      <c r="XDK25" s="1"/>
+      <c r="XDL25" s="1"/>
+      <c r="XDM25" s="1"/>
+      <c r="XDN25" s="1"/>
+      <c r="XDO25" s="1"/>
+      <c r="XDP25" s="1"/>
+      <c r="XDQ25" s="1"/>
+      <c r="XDR25" s="1"/>
+      <c r="XDS25" s="1"/>
+      <c r="XDT25" s="1"/>
+      <c r="XDU25" s="1"/>
+      <c r="XDV25" s="1"/>
+      <c r="XDW25" s="1"/>
+      <c r="XDX25" s="1"/>
+      <c r="XDY25" s="1"/>
+      <c r="XDZ25" s="1"/>
+      <c r="XEA25" s="1"/>
+      <c r="XEB25" s="1"/>
+      <c r="XEC25" s="1"/>
+      <c r="XED25" s="1"/>
+      <c r="XEE25" s="1"/>
+      <c r="XEF25" s="1"/>
+      <c r="XEG25" s="1"/>
+      <c r="XEH25" s="1"/>
+      <c r="XEI25" s="1"/>
+      <c r="XEJ25" s="1"/>
+      <c r="XEK25" s="1"/>
+      <c r="XEL25" s="1"/>
+      <c r="XEM25" s="1"/>
+      <c r="XEN25" s="1"/>
+      <c r="XEO25" s="1"/>
+      <c r="XEP25" s="1"/>
+      <c r="XEQ25" s="1"/>
+      <c r="XER25" s="1"/>
+      <c r="XES25" s="1"/>
+      <c r="XET25" s="1"/>
+      <c r="XEU25" s="1"/>
+      <c r="XEV25" s="1"/>
+      <c r="XEW25" s="1"/>
+      <c r="XEX25" s="1"/>
+      <c r="XEY25" s="1"/>
+      <c r="XEZ25" s="1"/>
+      <c r="XFA25" s="1"/>
+      <c r="XFB25" s="1"/>
+      <c r="XFC25" s="1"/>
+      <c r="XFD25" s="1"/>
+    </row>
+    <row r="26" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="XDH26" s="1"/>
+      <c r="XDI26" s="1"/>
+      <c r="XDJ26" s="1"/>
+      <c r="XDK26" s="1"/>
+      <c r="XDL26" s="1"/>
+      <c r="XDM26" s="1"/>
+      <c r="XDN26" s="1"/>
+      <c r="XDO26" s="1"/>
+      <c r="XDP26" s="1"/>
+      <c r="XDQ26" s="1"/>
+      <c r="XDR26" s="1"/>
+      <c r="XDS26" s="1"/>
+      <c r="XDT26" s="1"/>
+      <c r="XDU26" s="1"/>
+      <c r="XDV26" s="1"/>
+      <c r="XDW26" s="1"/>
+      <c r="XDX26" s="1"/>
+      <c r="XDY26" s="1"/>
+      <c r="XDZ26" s="1"/>
+      <c r="XEA26" s="1"/>
+      <c r="XEB26" s="1"/>
+      <c r="XEC26" s="1"/>
+      <c r="XED26" s="1"/>
+      <c r="XEE26" s="1"/>
+      <c r="XEF26" s="1"/>
+      <c r="XEG26" s="1"/>
+      <c r="XEH26" s="1"/>
+      <c r="XEI26" s="1"/>
+      <c r="XEJ26" s="1"/>
+      <c r="XEK26" s="1"/>
+      <c r="XEL26" s="1"/>
+      <c r="XEM26" s="1"/>
+      <c r="XEN26" s="1"/>
+      <c r="XEO26" s="1"/>
+      <c r="XEP26" s="1"/>
+      <c r="XEQ26" s="1"/>
+      <c r="XER26" s="1"/>
+      <c r="XES26" s="1"/>
+      <c r="XET26" s="1"/>
+      <c r="XEU26" s="1"/>
+      <c r="XEV26" s="1"/>
+      <c r="XEW26" s="1"/>
+      <c r="XEX26" s="1"/>
+      <c r="XEY26" s="1"/>
+      <c r="XEZ26" s="1"/>
+      <c r="XFA26" s="1"/>
+      <c r="XFB26" s="1"/>
+      <c r="XFC26" s="1"/>
+      <c r="XFD26" s="1"/>
+    </row>
+    <row r="27" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O27" s="1"/>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="XDH27" s="1"/>
+      <c r="XDI27" s="1"/>
+      <c r="XDJ27" s="1"/>
+      <c r="XDK27" s="1"/>
+      <c r="XDL27" s="1"/>
+      <c r="XDM27" s="1"/>
+      <c r="XDN27" s="1"/>
+      <c r="XDO27" s="1"/>
+      <c r="XDP27" s="1"/>
+      <c r="XDQ27" s="1"/>
+      <c r="XDR27" s="1"/>
+      <c r="XDS27" s="1"/>
+      <c r="XDT27" s="1"/>
+      <c r="XDU27" s="1"/>
+      <c r="XDV27" s="1"/>
+      <c r="XDW27" s="1"/>
+      <c r="XDX27" s="1"/>
+      <c r="XDY27" s="1"/>
+      <c r="XDZ27" s="1"/>
+      <c r="XEA27" s="1"/>
+      <c r="XEB27" s="1"/>
+      <c r="XEC27" s="1"/>
+      <c r="XED27" s="1"/>
+      <c r="XEE27" s="1"/>
+      <c r="XEF27" s="1"/>
+      <c r="XEG27" s="1"/>
+      <c r="XEH27" s="1"/>
+      <c r="XEI27" s="1"/>
+      <c r="XEJ27" s="1"/>
+      <c r="XEK27" s="1"/>
+      <c r="XEL27" s="1"/>
+      <c r="XEM27" s="1"/>
+      <c r="XEN27" s="1"/>
+      <c r="XEO27" s="1"/>
+      <c r="XEP27" s="1"/>
+      <c r="XEQ27" s="1"/>
+      <c r="XER27" s="1"/>
+      <c r="XES27" s="1"/>
+      <c r="XET27" s="1"/>
+      <c r="XEU27" s="1"/>
+      <c r="XEV27" s="1"/>
+      <c r="XEW27" s="1"/>
+      <c r="XEX27" s="1"/>
+      <c r="XEY27" s="1"/>
+      <c r="XEZ27" s="1"/>
+      <c r="XFA27" s="1"/>
+      <c r="XFB27" s="1"/>
+      <c r="XFC27" s="1"/>
+      <c r="XFD27" s="1"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
@@ -3259,50 +3952,50 @@
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10"/>
-      <c r="U35" s="10"/>
-      <c r="V35" s="10"/>
-      <c r="W35" s="10"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="11"/>
+      <c r="V35" s="11"/>
+      <c r="W35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="10"/>
-      <c r="S36" s="10"/>
-      <c r="T36" s="10"/>
-      <c r="U36" s="10"/>
-      <c r="V36" s="10"/>
-      <c r="W36" s="10"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
+      <c r="T36" s="11"/>
+      <c r="U36" s="11"/>
+      <c r="V36" s="11"/>
+      <c r="W36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
@@ -3384,50 +4077,50 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="10"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="10"/>
-      <c r="U40" s="10"/>
-      <c r="V40" s="10"/>
-      <c r="W40" s="10"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="11"/>
+      <c r="V40" s="11"/>
+      <c r="W40" s="11"/>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
-      <c r="U41" s="10"/>
-      <c r="V41" s="10"/>
-      <c r="W41" s="10"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="11"/>
+      <c r="V41" s="11"/>
+      <c r="W41" s="11"/>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
@@ -3534,375 +4227,375 @@
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="4"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="10"/>
-      <c r="S46" s="10"/>
-      <c r="T46" s="10"/>
-      <c r="U46" s="10"/>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
+      <c r="T46" s="11"/>
+      <c r="U46" s="11"/>
+      <c r="V46" s="11"/>
+      <c r="W46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="10"/>
-      <c r="U47" s="10"/>
-      <c r="V47" s="10"/>
-      <c r="W47" s="10"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="11"/>
+      <c r="Q47" s="11"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="11"/>
+      <c r="T47" s="11"/>
+      <c r="U47" s="11"/>
+      <c r="V47" s="11"/>
+      <c r="W47" s="11"/>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="10"/>
-      <c r="R48" s="10"/>
-      <c r="S48" s="10"/>
-      <c r="T48" s="10"/>
-      <c r="U48" s="10"/>
-      <c r="V48" s="10"/>
-      <c r="W48" s="10"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="11"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="11"/>
+      <c r="T48" s="11"/>
+      <c r="U48" s="11"/>
+      <c r="V48" s="11"/>
+      <c r="W48" s="11"/>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="10"/>
-      <c r="S49" s="10"/>
-      <c r="T49" s="10"/>
-      <c r="U49" s="10"/>
-      <c r="V49" s="10"/>
-      <c r="W49" s="10"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
+      <c r="T49" s="11"/>
+      <c r="U49" s="11"/>
+      <c r="V49" s="11"/>
+      <c r="W49" s="11"/>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="10"/>
-      <c r="R50" s="10"/>
-      <c r="S50" s="10"/>
-      <c r="T50" s="10"/>
-      <c r="U50" s="10"/>
-      <c r="V50" s="10"/>
-      <c r="W50" s="10"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="11"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="11"/>
+      <c r="T50" s="11"/>
+      <c r="U50" s="11"/>
+      <c r="V50" s="11"/>
+      <c r="W50" s="11"/>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10"/>
-      <c r="T51" s="10"/>
-      <c r="U51" s="10"/>
-      <c r="V51" s="10"/>
-      <c r="W51" s="10"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="11"/>
+      <c r="Q51" s="11"/>
+      <c r="R51" s="11"/>
+      <c r="S51" s="11"/>
+      <c r="T51" s="11"/>
+      <c r="U51" s="11"/>
+      <c r="V51" s="11"/>
+      <c r="W51" s="11"/>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
-      <c r="Q52" s="10"/>
-      <c r="R52" s="10"/>
-      <c r="S52" s="10"/>
-      <c r="T52" s="10"/>
-      <c r="U52" s="10"/>
-      <c r="V52" s="10"/>
-      <c r="W52" s="10"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="11"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
+      <c r="T52" s="11"/>
+      <c r="U52" s="11"/>
+      <c r="V52" s="11"/>
+      <c r="W52" s="11"/>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
+      <c r="T53" s="11"/>
+      <c r="U53" s="11"/>
+      <c r="V53" s="11"/>
+      <c r="W53" s="11"/>
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10"/>
-      <c r="R54" s="10"/>
-      <c r="S54" s="10"/>
-      <c r="T54" s="10"/>
-      <c r="U54" s="10"/>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="11"/>
+      <c r="R54" s="11"/>
+      <c r="S54" s="11"/>
+      <c r="T54" s="11"/>
+      <c r="U54" s="11"/>
+      <c r="V54" s="11"/>
+      <c r="W54" s="11"/>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="10"/>
-      <c r="S55" s="10"/>
-      <c r="T55" s="10"/>
-      <c r="U55" s="10"/>
-      <c r="V55" s="10"/>
-      <c r="W55" s="10"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="Q55" s="11"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="11"/>
+      <c r="T55" s="11"/>
+      <c r="U55" s="11"/>
+      <c r="V55" s="11"/>
+      <c r="W55" s="11"/>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
-      <c r="R56" s="10"/>
-      <c r="S56" s="10"/>
-      <c r="T56" s="10"/>
-      <c r="U56" s="10"/>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="11"/>
+      <c r="P56" s="11"/>
+      <c r="Q56" s="11"/>
+      <c r="R56" s="11"/>
+      <c r="S56" s="11"/>
+      <c r="T56" s="11"/>
+      <c r="U56" s="11"/>
+      <c r="V56" s="11"/>
+      <c r="W56" s="11"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
-      <c r="O57" s="10"/>
-      <c r="P57" s="10"/>
-      <c r="Q57" s="10"/>
-      <c r="R57" s="10"/>
-      <c r="S57" s="10"/>
-      <c r="T57" s="10"/>
-      <c r="U57" s="10"/>
-      <c r="V57" s="10"/>
-      <c r="W57" s="10"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="11"/>
+      <c r="R57" s="11"/>
+      <c r="S57" s="11"/>
+      <c r="T57" s="11"/>
+      <c r="U57" s="11"/>
+      <c r="V57" s="11"/>
+      <c r="W57" s="11"/>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10"/>
-      <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
-      <c r="Q58" s="10"/>
-      <c r="R58" s="10"/>
-      <c r="S58" s="10"/>
-      <c r="T58" s="10"/>
-      <c r="U58" s="10"/>
-      <c r="V58" s="10"/>
-      <c r="W58" s="10"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="11"/>
+      <c r="O58" s="11"/>
+      <c r="P58" s="11"/>
+      <c r="Q58" s="11"/>
+      <c r="R58" s="11"/>
+      <c r="S58" s="11"/>
+      <c r="T58" s="11"/>
+      <c r="U58" s="11"/>
+      <c r="V58" s="11"/>
+      <c r="W58" s="11"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
-      <c r="N59" s="10"/>
-      <c r="O59" s="10"/>
-      <c r="P59" s="10"/>
-      <c r="Q59" s="10"/>
-      <c r="R59" s="10"/>
-      <c r="S59" s="10"/>
-      <c r="T59" s="10"/>
-      <c r="U59" s="10"/>
-      <c r="V59" s="10"/>
-      <c r="W59" s="10"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="11"/>
+      <c r="O59" s="11"/>
+      <c r="P59" s="11"/>
+      <c r="Q59" s="11"/>
+      <c r="R59" s="11"/>
+      <c r="S59" s="11"/>
+      <c r="T59" s="11"/>
+      <c r="U59" s="11"/>
+      <c r="V59" s="11"/>
+      <c r="W59" s="11"/>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="7"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10"/>
-      <c r="O60" s="10"/>
-      <c r="P60" s="10"/>
-      <c r="Q60" s="10"/>
-      <c r="R60" s="10"/>
-      <c r="S60" s="10"/>
-      <c r="T60" s="10"/>
-      <c r="U60" s="10"/>
-      <c r="V60" s="10"/>
-      <c r="W60" s="10"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="11"/>
+      <c r="O60" s="11"/>
+      <c r="P60" s="11"/>
+      <c r="Q60" s="11"/>
+      <c r="R60" s="11"/>
+      <c r="S60" s="11"/>
+      <c r="T60" s="11"/>
+      <c r="U60" s="11"/>
+      <c r="V60" s="11"/>
+      <c r="W60" s="11"/>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
@@ -5581,7 +6274,7 @@
     </row>
     <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3"/>
-      <c r="B128" s="11"/>
+      <c r="B128" s="12"/>
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -6906,7 +7599,7 @@
     </row>
     <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3"/>
-      <c r="B181" s="12"/>
+      <c r="B181" s="13"/>
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -7056,7 +7749,7 @@
     </row>
     <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3"/>
-      <c r="B187" s="12"/>
+      <c r="B187" s="13"/>
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -7081,7 +7774,7 @@
     </row>
     <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3"/>
-      <c r="B188" s="12"/>
+      <c r="B188" s="13"/>
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -7106,7 +7799,7 @@
     </row>
     <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3"/>
-      <c r="B189" s="12"/>
+      <c r="B189" s="13"/>
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -16455,7 +17148,7 @@
       <c r="W562" s="4"/>
     </row>
     <row r="563" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A563" s="13"/>
+      <c r="A563" s="14"/>
       <c r="B563" s="4"/>
       <c r="C563" s="4"/>
       <c r="D563" s="4"/>
@@ -16480,7 +17173,7 @@
       <c r="W563" s="4"/>
     </row>
     <row r="564" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A564" s="13"/>
+      <c r="A564" s="14"/>
       <c r="B564" s="4"/>
       <c r="C564" s="4"/>
       <c r="D564" s="4"/>
@@ -18856,7 +19549,7 @@
     </row>
     <row r="659" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="3"/>
-      <c r="B659" s="12"/>
+      <c r="B659" s="13"/>
       <c r="C659" s="4"/>
       <c r="D659" s="4"/>
       <c r="E659" s="4"/>
@@ -18881,7 +19574,7 @@
     </row>
     <row r="660" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="3"/>
-      <c r="B660" s="14"/>
+      <c r="B660" s="15"/>
       <c r="C660" s="4"/>
       <c r="D660" s="4"/>
       <c r="E660" s="4"/>
@@ -19805,7 +20498,7 @@
       <c r="W696" s="4"/>
     </row>
     <row r="697" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A697" s="15"/>
+      <c r="A697" s="16"/>
       <c r="B697" s="4"/>
       <c r="C697" s="4"/>
       <c r="D697" s="4"/>
